--- a/artfynd/A 58191-2022 artfynd.xlsx
+++ b/artfynd/A 58191-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58191-2022 artfynd.xlsx
+++ b/artfynd/A 58191-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111487425</v>
+        <v>111487426</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Armsjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626157.6942840694</v>
+        <v>626134</v>
       </c>
       <c r="R2" t="n">
-        <v>6893095.882089161</v>
+        <v>6893051</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,28 +743,17 @@
           <t>2023-07-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111487426</v>
+        <v>111487427</v>
       </c>
       <c r="B3" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626133.5793112689</v>
+        <v>626206</v>
       </c>
       <c r="R3" t="n">
-        <v>6893051.461214696</v>
+        <v>6893112</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +840,9 @@
           <t>2023-07-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,6 +866,308 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111487425</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Armsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>626158</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6893096</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111487424</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Armsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>626179</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6893140</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111487428</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Armsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>626201</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6893121</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter spridda över 2 m2</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58191-2022 artfynd.xlsx
+++ b/artfynd/A 58191-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111487426</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111487427</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111487425</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111487424</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1168,8 +1193,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111487428</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>